--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428403</v>
+        <v>122428555</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562810</v>
+        <v>562846</v>
       </c>
       <c r="R2" t="n">
-        <v>7039408</v>
+        <v>7039370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428555</v>
+        <v>122428403</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -833,19 +833,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562846</v>
+        <v>562810</v>
       </c>
       <c r="R3" t="n">
-        <v>7039370</v>
+        <v>7039408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,12 +907,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428555</v>
+        <v>122428403</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562846</v>
+        <v>562810</v>
       </c>
       <c r="R2" t="n">
-        <v>7039370</v>
+        <v>7039408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428403</v>
+        <v>122428417</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562810</v>
+        <v>562839</v>
       </c>
       <c r="R3" t="n">
-        <v>7039408</v>
+        <v>7039358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428417</v>
+        <v>122428555</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562839</v>
+        <v>562846</v>
       </c>
       <c r="R4" t="n">
-        <v>7039358</v>
+        <v>7039370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428403</v>
+        <v>122428555</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562810</v>
+        <v>562846</v>
       </c>
       <c r="R2" t="n">
-        <v>7039408</v>
+        <v>7039370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428555</v>
+        <v>122428403</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -955,19 +955,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562846</v>
+        <v>562810</v>
       </c>
       <c r="R4" t="n">
-        <v>7039370</v>
+        <v>7039408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428555</v>
+        <v>122428417</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562846</v>
+        <v>562839</v>
       </c>
       <c r="R2" t="n">
-        <v>7039370</v>
+        <v>7039358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428417</v>
+        <v>122428403</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -815,11 +810,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -833,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562839</v>
+        <v>562810</v>
       </c>
       <c r="R3" t="n">
-        <v>7039358</v>
+        <v>7039408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428403</v>
+        <v>122428555</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -937,11 +927,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -955,19 +940,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562810</v>
+        <v>562846</v>
       </c>
       <c r="R4" t="n">
-        <v>7039408</v>
+        <v>7039370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +1014,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428417</v>
+        <v>122428555</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -715,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562839</v>
+        <v>562846</v>
       </c>
       <c r="R2" t="n">
-        <v>7039358</v>
+        <v>7039370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +800,7 @@
         <v>122428403</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,6 +814,11 @@
       </c>
       <c r="E3" t="n">
         <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428555</v>
+        <v>122428417</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,6 +937,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -949,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562846</v>
+        <v>562839</v>
       </c>
       <c r="R4" t="n">
-        <v>7039370</v>
+        <v>7039358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428403</v>
+        <v>122428417</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -833,19 +833,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562810</v>
+        <v>562839</v>
       </c>
       <c r="R3" t="n">
-        <v>7039408</v>
+        <v>7039358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,19 +907,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428417</v>
+        <v>122428403</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -955,19 +955,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562839</v>
+        <v>562810</v>
       </c>
       <c r="R4" t="n">
-        <v>7039358</v>
+        <v>7039408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428555</v>
+        <v>122428403</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562846</v>
+        <v>562810</v>
       </c>
       <c r="R2" t="n">
-        <v>7039370</v>
+        <v>7039408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428403</v>
+        <v>122428555</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -955,19 +955,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562810</v>
+        <v>562846</v>
       </c>
       <c r="R4" t="n">
-        <v>7039408</v>
+        <v>7039370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428403</v>
+        <v>122428417</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562810</v>
+        <v>562839</v>
       </c>
       <c r="R2" t="n">
-        <v>7039408</v>
+        <v>7039358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428417</v>
+        <v>122428403</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -833,19 +833,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562839</v>
+        <v>562810</v>
       </c>
       <c r="R3" t="n">
-        <v>7039358</v>
+        <v>7039408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,12 +907,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428417</v>
+        <v>122428403</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562839</v>
+        <v>562810</v>
       </c>
       <c r="R2" t="n">
-        <v>7039358</v>
+        <v>7039408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428403</v>
+        <v>122428417</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -833,19 +833,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562810</v>
+        <v>562839</v>
       </c>
       <c r="R3" t="n">
-        <v>7039408</v>
+        <v>7039358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,12 +907,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428403</v>
+        <v>122428417</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562810</v>
+        <v>562839</v>
       </c>
       <c r="R2" t="n">
-        <v>7039408</v>
+        <v>7039358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428417</v>
+        <v>122428555</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562839</v>
+        <v>562846</v>
       </c>
       <c r="R3" t="n">
-        <v>7039358</v>
+        <v>7039370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428555</v>
+        <v>122428403</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,19 +955,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562846</v>
+        <v>562810</v>
       </c>
       <c r="R4" t="n">
-        <v>7039370</v>
+        <v>7039408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122428555</v>
+        <v>122428403</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -833,19 +833,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollklippen, Trollklippen, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562846</v>
+        <v>562810</v>
       </c>
       <c r="R3" t="n">
-        <v>7039370</v>
+        <v>7039408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,19 +907,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428403</v>
+        <v>122428555</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -955,19 +955,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562810</v>
+        <v>562846</v>
       </c>
       <c r="R4" t="n">
-        <v>7039408</v>
+        <v>7039370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 45085-2022 artfynd.xlsx
+++ b/artfynd/A 45085-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122428417</v>
+        <v>122428555</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562839</v>
+        <v>562846</v>
       </c>
       <c r="R2" t="n">
-        <v>7039358</v>
+        <v>7039370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122428555</v>
+        <v>122428417</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562846</v>
+        <v>562839</v>
       </c>
       <c r="R4" t="n">
-        <v>7039370</v>
+        <v>7039358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
